--- a/output/pdf_financials_xlsx/HARY.xlsx
+++ b/output/pdf_financials_xlsx/HARY.xlsx
@@ -1922,13 +1922,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.035256</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.174056</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.180336</v>
       </c>
     </row>
     <row r="93">
@@ -3100,7 +3100,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>4.035256</v>
       </c>

--- a/output/pdf_financials_xlsx/HARY.xlsx
+++ b/output/pdf_financials_xlsx/HARY.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.36579</v>
+        <v>0.598621</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.232525</v>
+        <v>0.518709</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.392677</v>
+        <v>0.525699</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.368872</v>
+        <v>-0.601703</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.239379</v>
+        <v>-0.525563</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.388464</v>
+        <v>-0.521486</v>
       </c>
     </row>
     <row r="12">
@@ -970,13 +970,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.016869</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.01084</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.059014</v>
       </c>
     </row>
     <row r="35">
@@ -1002,13 +1002,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.016869</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.01084</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.059014</v>
       </c>
     </row>
     <row r="37">
@@ -1194,13 +1194,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.075532</v>
+        <v>0.058663</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.012695</v>
+        <v>0.001855</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.059014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>-0.598621</v>
+        <v>0.598621</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>-0.518709</v>
+        <v>0.518709</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.525699</v>
+        <v>0.525699</v>
       </c>
     </row>
     <row r="56">
@@ -5205,7 +5205,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">

--- a/output/pdf_financials_xlsx/HARY.xlsx
+++ b/output/pdf_financials_xlsx/HARY.xlsx
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.242276</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.410265</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.495496</v>
       </c>
     </row>
     <row r="65">
@@ -1504,13 +1504,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.041769</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07832500000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.343774</v>
       </c>
     </row>
     <row r="68">
@@ -2030,10 +2030,8 @@
       <c r="C99" s="3" t="n">
         <v>-0.515563</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-0.436191</v>
       </c>
     </row>
     <row r="100">
@@ -2048,10 +2046,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2066,10 +2062,8 @@
       <c r="C101" s="3" t="n">
         <v>-0.015028</v>
       </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D101" s="3" t="n">
+        <v>0.021568</v>
       </c>
     </row>
     <row r="102">
@@ -2084,10 +2078,8 @@
       <c r="C102" s="3" t="n">
         <v>0.000346</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2102,10 +2094,8 @@
       <c r="C103" s="3" t="n">
         <v>0.026808</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>0.001855</v>
       </c>
     </row>
     <row r="104">
@@ -2120,10 +2110,8 @@
       <c r="C104" s="3" t="n">
         <v>0.204545</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.47253</v>
       </c>
     </row>
     <row r="105">
@@ -2138,10 +2126,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2156,10 +2142,8 @@
       <c r="C106" s="3" t="n">
         <v>0.216671</v>
       </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D106" s="3" t="n">
+        <v>0.495953</v>
       </c>
     </row>
     <row r="107">
@@ -2174,10 +2158,8 @@
       <c r="C107" s="3" t="n">
         <v>0.134</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2192,10 +2174,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2210,10 +2190,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2228,10 +2206,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2246,10 +2222,8 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2264,10 +2238,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2282,10 +2254,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2300,10 +2270,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2318,10 +2286,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2336,10 +2302,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2354,10 +2318,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2372,10 +2334,8 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2390,10 +2350,8 @@
       <c r="C119" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2408,10 +2366,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2426,10 +2382,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2444,10 +2398,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2462,10 +2414,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2480,10 +2430,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2498,10 +2446,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2516,10 +2462,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2556,10 +2500,8 @@
       <c r="C128" s="3" t="n">
         <v>-0.004798</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>-0.00115</v>
       </c>
     </row>
     <row r="129">
@@ -2574,10 +2516,8 @@
       <c r="C129" s="3" t="n">
         <v>0.157172</v>
       </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D129" s="3" t="n">
+        <v>0.07285</v>
       </c>
     </row>
     <row r="130">
@@ -2592,10 +2532,8 @@
       <c r="C130" s="3" t="n">
         <v>0.016869</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.01084</v>
       </c>
     </row>
     <row r="131">
@@ -2610,10 +2548,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2628,10 +2564,8 @@
       <c r="C132" s="3" t="n">
         <v>-0.006029</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>0.048174</v>
       </c>
     </row>
     <row r="133">
@@ -2646,10 +2580,8 @@
       <c r="C133" s="3" t="n">
         <v>0.01084</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.059014</v>
       </c>
     </row>
     <row r="134">
@@ -2664,10 +2596,8 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2682,10 +2612,8 @@
       <c r="C135" s="3" t="n">
         <v>-0.163201</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.024676</v>
       </c>
     </row>
   </sheetData>
@@ -2699,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3332,10 +3260,8 @@
       <c r="F20" s="5" t="n">
         <v>-0.515563</v>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="5" t="n">
+        <v>-0.436191</v>
       </c>
     </row>
     <row r="21">
@@ -3351,22 +3277,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accretion and interest</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
-        <v>0.000724</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001692</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.001691</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.000857</v>
       </c>
     </row>
     <row r="22">
@@ -3382,24 +3308,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.001692</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.001691</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gain on settlement of debt</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-0.085295</v>
       </c>
     </row>
     <row r="23">
@@ -3443,27 +3367,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Adjustment for non-cash items</t>
+          <t>Changes in non-cash operating working capital items</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Loss on conversion of convertible debt</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>0.087717</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.007594</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-0.015028</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.021568</v>
       </c>
     </row>
     <row r="25">
@@ -3479,19 +3403,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Amounts receivable</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ChangeInReceivables</t>
+          <t>ChangeInInventory</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>-0.007594</v>
+        <v>-0.000346</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>-0.015028</v>
+        <v>0.000346</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -3512,24 +3436,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Inventory</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ChangeInInventory</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-0.000346</v>
+        <v>0.008723</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.000346</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.026808</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.001855</v>
       </c>
     </row>
     <row r="27">
@@ -3545,24 +3467,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.008723</v>
+        <v>0.20071</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.026808</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.204545</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.47253</v>
       </c>
     </row>
     <row r="28">
@@ -3578,24 +3498,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.20071</v>
+        <v>-0.264371</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.204545</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.163201</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-0.024676</v>
       </c>
     </row>
     <row r="29">
@@ -3606,29 +3524,25 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash operating working capital items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>-0.264371</v>
+          <t>Proceeds received from share issuances</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-0.163201</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.14997</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.074</v>
       </c>
     </row>
     <row r="30">
@@ -3639,27 +3553,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Redemption of deposit</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-0.004798</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-0.00115</v>
       </c>
     </row>
     <row r="31">
@@ -3670,26 +3586,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash provided by investing activities</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Subscriptions received in advance</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3710,22 +3622,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of warrants</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E32" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.157172</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.07285</v>
       </c>
     </row>
     <row r="33">
@@ -3741,26 +3653,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Proceeds from exercise of options</t>
+          <t>Change in cash</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>IssuanceOfCapitalStock</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.007629</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-0.006029</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.048174</v>
       </c>
     </row>
     <row r="34">
@@ -3776,22 +3684,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds received from share issuances</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash, beginning of year</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.00924</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.14997</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016869</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.01084</v>
       </c>
     </row>
     <row r="35">
@@ -3807,26 +3715,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
+          <t>Cash, end of year</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.016869</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.004798</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01084</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.059014</v>
       </c>
     </row>
     <row r="36">
@@ -3837,12 +3741,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance</t>
+          <t>Shares issued on settlement of debt</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3851,13 +3755,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F36" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.036555</v>
       </c>
     </row>
     <row r="37">
@@ -3868,29 +3772,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0.157172</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Fair value allocated to warrants</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.00628</v>
       </c>
     </row>
     <row r="38">
@@ -3901,24 +3803,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Supplementary cash flow information</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Change in cash</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0.007629</v>
+          <t>Fair value of brokers’ warrants</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.006029</v>
+        <v>0.0048</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -3934,24 +3834,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustment for non-cash items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Accretion and interest</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>0.00924</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>0.016869</v>
+        <v>0.000724</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -3967,24 +3865,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Adjustment for non-cash items</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash, end of year</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Loss on conversion of convertible debt</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" s="5" t="n">
-        <v>0.016869</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>0.01084</v>
+        <v>0.087717</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -4000,17 +3896,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Units issued on settlement of debt</t>
+          <t>Redemption of deposit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>0.348742</v>
+        <v>0.2</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4031,22 +3927,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Supplementary cash flow information</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Fair value of brokers’ warrants</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0.0048</v>
+          <t>Net cash provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4057,84 +3957,98 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Revenue (Note 4)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.04812</v>
-      </c>
-      <c r="G43" s="5" t="n">
-        <v>0.04216</v>
+          <t>Proceeds from exercise of warrants</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Proceeds from exercise of options</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.054974</v>
-      </c>
-      <c r="G44" s="5" t="n">
-        <v>0.037947</v>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supplementary cash flow information</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Gross income</t>
+          <t>Units issued on settlement of debt</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="n">
-        <v>-0.006854</v>
-      </c>
-      <c r="G45" s="5" t="n">
-        <v>0.004213</v>
+      <c r="E45" s="5" t="n">
+        <v>0.348742</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -4143,29 +4057,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Amortization and depreciation</t>
+          <t>Revenue (Note 4)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DepreciationAndAmortization</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>0.001692</v>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.001691</v>
+        <v>0.04812</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.000857</v>
+        <v>0.04216</v>
       </c>
     </row>
     <row r="47">
@@ -4174,19 +4086,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 7)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4195,10 +4103,10 @@
         </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.024148</v>
+        <v>0.054974</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.086108</v>
+        <v>0.037947</v>
       </c>
     </row>
     <row r="48">
@@ -4207,29 +4115,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Management fees (Note 7)</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.240069</v>
+          <t>Gross income</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.1375</v>
+        <v>-0.006854</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.26</v>
+        <v>0.004213</v>
       </c>
     </row>
     <row r="49">
@@ -4245,22 +4147,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Office and administrative</t>
+          <t>Amortization and depreciation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>DepreciationAndAmortization</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.07130300000000001</v>
+        <v>0.001692</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.040686</v>
+        <v>0.001691</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.022897</v>
+        <v>0.000857</v>
       </c>
     </row>
     <row r="50">
@@ -4276,12 +4178,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Consulting fees (Note 7)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4290,10 +4192,10 @@
         </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.150493</v>
+        <v>0.024148</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.132165</v>
+        <v>0.086108</v>
       </c>
     </row>
     <row r="51">
@@ -4309,20 +4211,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
-        <v>0.09414699999999999</v>
+        <v>0.240069</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.1375</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.26</v>
       </c>
     </row>
     <row r="52">
@@ -4338,7 +4242,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Shareholder communications</t>
+          <t>Office and administrative</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4347,13 +4251,13 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.007637</v>
+        <v>0.07130300000000001</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.007247</v>
+        <v>0.040686</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.001166</v>
+        <v>0.022897</v>
       </c>
     </row>
     <row r="53">
@@ -4369,22 +4273,24 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.036823</v>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.019553</v>
+        <v>0.150493</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.021586</v>
+        <v>0.132165</v>
       </c>
     </row>
     <row r="54">
@@ -4400,22 +4306,20 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share-based payments (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.009958</v>
+        <v>0.09414699999999999</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.003391</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0.00092</v>
+        <v>0.134</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -4431,22 +4335,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Total expenses</t>
+          <t>Shareholder communications</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.598621</v>
+        <v>0.007637</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.518709</v>
+        <v>0.007247</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.525699</v>
+        <v>0.001166</v>
       </c>
     </row>
     <row r="56">
@@ -4462,24 +4366,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Net loss before other income</t>
+          <t>Transfer agent and filing fees</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>0.036823</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>-0.525563</v>
+        <v>0.019553</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.521486</v>
+        <v>0.021586</v>
       </c>
     </row>
     <row r="57">
@@ -4490,27 +4392,27 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Recovery of expenses (Note 5)</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>0.009958</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.003391</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.00092</v>
       </c>
     </row>
     <row r="58">
@@ -4521,27 +4423,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gain on settlement of debt (Note 7)</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>0.598621</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.518709</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.085295</v>
+        <v>0.525699</v>
       </c>
     </row>
     <row r="59">
@@ -4552,17 +4454,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Net loss before other income</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4571,10 +4473,10 @@
         </is>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-0.515563</v>
+        <v>-0.525563</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.436191</v>
+        <v>-0.521486</v>
       </c>
     </row>
     <row r="60">
@@ -4590,24 +4492,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Recovery of expenses (Note 5)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -4623,24 +4523,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Gain on settlement of debt (Note 7)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F61" s="5" t="n">
-        <v>98.734469</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" s="5" t="n">
-        <v>104.636525</v>
+        <v>0.085295</v>
       </c>
     </row>
     <row r="62">
@@ -4651,23 +4549,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance, as at July 31, 2023 95,336,126 21,826,448 4,035,256 –</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>-0.24278</v>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-0.24278</v>
+        <v>-0.515563</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-26.104484</v>
+        <v>-0.436191</v>
       </c>
     </row>
     <row r="63">
@@ -4678,25 +4582,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Units issued on private placements 5,498,999 149,970 – –</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" s="5" t="n">
-        <v>0.14997</v>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.14997</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4707,25 +4615,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share issuance costs – (9,598) 4,800 –</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>-0.004798</v>
+          <t>Weighted average common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F64" s="5" t="n">
-        <v>-0.004798</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>98.734469</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>104.636525</v>
       </c>
     </row>
     <row r="65">
@@ -4741,20 +4653,18 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share-based payments – – 134,000 –</t>
+          <t>Balance, as at July 31, 2023 95,336,126 21,826,448 4,035,256 –</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.134</v>
+        <v>-0.24278</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.24278</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-26.104484</v>
       </c>
     </row>
     <row r="66">
@@ -4770,15 +4680,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Subscriptions received in advance – – – 12,000</t>
+          <t>Units issued on private placements 5,498,999 149,970 – –</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>0.012</v>
+        <v>0.14997</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.012</v>
+        <v>0.14997</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4799,22 +4709,20 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss for the year – – – –</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs – (9,598) 4,800 –</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" s="5" t="n">
-        <v>-0.6501440000000001</v>
+        <v>-0.004798</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>-0.515563</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>-0.515563</v>
+        <v>-0.004798</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4830,18 +4738,20 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Balance, as at July 31, 2024 100,835,125 21,966,820 4,174,056 12,000</t>
+          <t>Share-based payments – – 134,000 –</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" s="5" t="n">
-        <v>-0.467171</v>
+        <v>0.134</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.467171</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>-26.620047</v>
+        <v>0.134</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4857,17 +4767,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Units issued on private placements 3,986,957 79,720 6,280 (12,000)</t>
+          <t>Subscriptions received in advance – – – 12,000</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E69" s="5" t="n">
+        <v>0.012</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.074</v>
+        <v>0.012</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4888,22 +4796,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Share issuance costs – (1,150) – –</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss for the year – – – –</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="n">
+        <v>-0.6501440000000001</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.00115</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.515563</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-0.515563</v>
       </c>
     </row>
     <row r="71">
@@ -4919,22 +4827,18 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement 2,437,000 36,555 – –</t>
+          <t>Balance, as at July 31, 2024 100,835,125 21,966,820 4,174,056 12,000</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E71" s="5" t="n">
+        <v>-0.467171</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.036555</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.467171</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-26.620047</v>
       </c>
     </row>
     <row r="72">
@@ -4950,7 +4854,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Balance, as at July 31, 2025 107,259,082 22,081,945 4,180,336 –</t>
+          <t>Units issued on private placements 3,986,957 79,720 6,280 (12,000)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
@@ -4960,10 +4864,12 @@
         </is>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-0.793957</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>-27.056238</v>
+        <v>0.074</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4974,24 +4880,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ended July 31, ended July 31,</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Revenue (Note 4)</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0.023496</v>
+          <t>Share issuance costs – (1,150) – –</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.04812</v>
+        <v>-0.00115</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5007,24 +4911,22 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ended July 31, ended July 31,</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>0.026578</v>
+          <t>Shares issued for debt settlement 2,437,000 36,555 – –</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.054974</v>
+        <v>0.036555</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5040,25 +4942,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ended July 31, ended July 31,</t>
+          <t>#</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Gross loss</t>
+          <t>Balance, as at July 31, 2025 107,259,082 22,081,945 4,180,336 –</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>-0.003082</v>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.006854</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.793957</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>-27.056238</v>
       </c>
     </row>
     <row r="76">
@@ -5069,22 +4971,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>ended July 31, ended July 31,</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bad debt expense (Note 4)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>Revenue (Note 4)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.023496</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>0.04812</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5100,24 +5004,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>ended July 31, ended July 31,</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Professional fees (Note 7)</t>
+          <t>Cost of sales</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0.123692</v>
+        <v>0.026578</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.150493</v>
+        <v>0.054974</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5133,24 +5037,20 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>ended July 31, ended July 31,</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net loss before other income (expense)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Gross loss</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" s="5" t="n">
-        <v>-0.601703</v>
+        <v>-0.003082</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.525563</v>
+        <v>-0.006854</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5166,20 +5066,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Recovery of expenses (Note 5)</t>
+          <t>Bad debt expense (Note 4)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>0.01</v>
+        <v>0.0133</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5195,26 +5097,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Professional fees (Note 7)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>-0.000724</v>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.123692</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.150493</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5230,22 +5130,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Other income (expense)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Loss on settlement of debt (Notes 7 and 8)</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Net loss before other income (expense)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
-        <v>-0.087717</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.601703</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.525563</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5266,19 +5168,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Recovery of expenses (Note 5)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
-        <v>-0.6501440000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>-0.515563</v>
+        <v>0.01</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5299,19 +5197,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
+          <t>Interest expense</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.000724</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5332,19 +5232,17 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Loss on settlement of debt (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" s="5" t="n">
-        <v>93.87805299999999</v>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>98.734469</v>
+        <v>-0.087717</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5360,20 +5258,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Balance, as at July 31, 2022 90,770,007 21,420,202 3,926,613 –</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Net loss and comprehensive loss</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E85" s="5" t="n">
-        <v>-0.107525</v>
+        <v>-0.6501440000000001</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-25.45434</v>
+        <v>-0.515563</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5389,22 +5291,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Units issued on settlement of debt 3,866,119 296,664 52,078 –</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
-        <v>0.348742</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5420,22 +5324,24 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>Other income (expense)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Shares issued upon the exercise of warrants 500,000 67,500 (17,500) –</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Weighted average common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>93.87805299999999</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>98.734469</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5456,17 +5362,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Share-based payments – – 94,147 –</t>
+          <t>Balance, as at July 31, 2022 90,770,007 21,420,202 3,926,613 –</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" s="5" t="n">
-        <v>0.09414699999999999</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.107525</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-25.45434</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5487,19 +5391,112 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shares issued upon the exercise of options 200,000 42,082 (20,082) –</t>
+          <t>Units issued on settlement of debt 3,866,119 296,664 52,078 –</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" s="5" t="n">
+        <v>0.348742</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Shares issued upon the exercise of warrants 500,000 67,500 (17,500) –</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Share-based payments – – 94,147 –</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" s="5" t="n">
+        <v>0.09414699999999999</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Shares issued upon the exercise of options 200,000 42,082 (20,082) –</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
         <v>0.022</v>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
